--- a/artfynd/A 26675-2023 artfynd.xlsx
+++ b/artfynd/A 26675-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26675-2023 artfynd.xlsx
+++ b/artfynd/A 26675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88571511</v>
+        <v>88571503</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527314.6207468818</v>
+        <v>527055</v>
       </c>
       <c r="R2" t="n">
-        <v>6908114.418555153</v>
+        <v>6908194</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88571512</v>
+        <v>88571506</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527311.8372258882</v>
+        <v>527213</v>
       </c>
       <c r="R3" t="n">
-        <v>6908113.00039668</v>
+        <v>6908214</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,24 +840,9 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,58 +869,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88571507</v>
+        <v>112182932</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Riberget, Hls</t>
+          <t>Nylandet, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527166.2273720505</v>
+        <v>527229</v>
       </c>
       <c r="R4" t="n">
-        <v>6908203.454962526</v>
+        <v>6908168</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +938,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,27 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88571504</v>
+        <v>88571512</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,43 +986,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527141.9982070191</v>
+        <v>527312</v>
       </c>
       <c r="R5" t="n">
-        <v>6908204.189187867</v>
+        <v>6908113</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,19 +1043,14 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,50 +1077,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88571503</v>
+        <v>88571509</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527054.9722374964</v>
+        <v>527208</v>
       </c>
       <c r="R6" t="n">
-        <v>6908193.718099114</v>
+        <v>6908225</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,19 +1149,14 @@
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-07-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppflog. Flera kraftigt tjäderbetade tallar i närområdet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,57 +1183,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112182932</v>
+        <v>88571502</v>
       </c>
       <c r="B7" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nylandet, Hls</t>
+          <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527229</v>
+        <v>527072</v>
       </c>
       <c r="R7" t="n">
-        <v>6908169</v>
+        <v>6908258</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,17 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1273,320 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88571504</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527142</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6908204</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88571507</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527166</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6908203</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88571511</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527315</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6908114</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26675-2023 artfynd.xlsx
+++ b/artfynd/A 26675-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571506</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182932</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571504</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571507</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,8 +1632,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>